--- a/data/trans_orig/P04D$aparatos-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>686792</t>
+          <t>687493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>743754</t>
+          <t>743852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>935990</t>
+          <t>936918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1002538</t>
+          <t>1000628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1641583</t>
+          <t>1642012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1731488</t>
+          <t>1731713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>35879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48686</t>
+          <t>49969</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173347</t>
+          <t>171547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224349</t>
+          <t>224352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>247332</t>
+          <t>247026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305037</t>
+          <t>305955</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>433266</t>
+          <t>432370</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>512674</t>
+          <t>512664</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66155</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>59278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>94231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106861</t>
+          <t>105242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150187</t>
+          <t>147964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1162627</t>
+          <t>1159409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1252836</t>
+          <t>1251990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1050780</t>
+          <t>1053440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1137008</t>
+          <t>1134474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2239888</t>
+          <t>2240524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2357681</t>
+          <t>2359704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,56%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52088</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85400</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,47 +1316,47 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>46725</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>34596</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>62566</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>46725</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>34204</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>62914</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92502</t>
+          <t>93732</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>136493</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>568356</t>
+          <t>569145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>651700</t>
+          <t>656831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>505484</t>
+          <t>507898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>585716</t>
+          <t>589311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1100055</t>
+          <t>1099704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1213110</t>
+          <t>1216009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62755</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>100173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57731</t>
+          <t>57759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92915</t>
+          <t>93195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128952</t>
+          <t>129786</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180419</t>
+          <t>178446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>209186</t>
+          <t>211979</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>256384</t>
+          <t>259054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221264</t>
+          <t>221471</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>268555</t>
+          <t>268407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>443611</t>
+          <t>446695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>509132</t>
+          <t>510923</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43345</t>
+          <t>41745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71831</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185504</t>
+          <t>183537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233071</t>
+          <t>229713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163527</t>
+          <t>160556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208484</t>
+          <t>208512</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360249</t>
+          <t>358819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>425037</t>
+          <t>424221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2100456</t>
+          <t>2101717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2215281</t>
+          <t>2215920</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2245067</t>
+          <t>2249892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2364997</t>
+          <t>2369972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4374508</t>
+          <t>4383390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4541021</t>
+          <t>4550326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88019</t>
+          <t>89084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129517</t>
+          <t>131649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77861</t>
+          <t>77250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117170</t>
+          <t>117264</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175764</t>
+          <t>176731</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233441</t>
+          <t>233635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>958811</t>
+          <t>959363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1068667</t>
+          <t>1068243</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>951011</t>
+          <t>949606</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1061096</t>
+          <t>1058428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1940384</t>
+          <t>1939503</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2110292</t>
+          <t>2097597</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120450</t>
+          <t>117707</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169175</t>
+          <t>169531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135233</t>
+          <t>135971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>187003</t>
+          <t>187489</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>269765</t>
+          <t>268874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337085</t>
+          <t>341986</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>434647</t>
+          <t>430610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>488439</t>
+          <t>484584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>534124</t>
+          <t>537821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>601799</t>
+          <t>602659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>988801</t>
+          <t>986725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1075032</t>
+          <t>1068372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,08%</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27885</t>
+          <t>26736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107172</t>
+          <t>107717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147936</t>
+          <t>145310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>180278</t>
+          <t>182869</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>235868</t>
+          <t>235142</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>299430</t>
+          <t>303407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>370734</t>
+          <t>371542</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141918</t>
+          <t>142334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188644</t>
+          <t>189113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182182</t>
+          <t>180077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234599</t>
+          <t>233633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339471</t>
+          <t>336252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408032</t>
+          <t>404797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1025074</t>
+          <t>1026113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1115790</t>
+          <t>1120548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>990658</t>
+          <t>989696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1081348</t>
+          <t>1077022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2042378</t>
+          <t>2048596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2164216</t>
+          <t>2174519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64563</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>51508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>69260</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>106739</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>593809</t>
+          <t>595116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>678744</t>
+          <t>679906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>633261</t>
+          <t>634146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>721174</t>
+          <t>720271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1254676</t>
+          <t>1253508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1370094</t>
+          <t>1374992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282042</t>
+          <t>287533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>354716</t>
+          <t>354680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218564</t>
+          <t>217305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278956</t>
+          <t>278738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>520659</t>
+          <t>519531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>610597</t>
+          <t>609436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>228553</t>
+          <t>230561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>278646</t>
+          <t>279126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224205</t>
+          <t>224279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>272039</t>
+          <t>269498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>470458</t>
+          <t>468928</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>535387</t>
+          <t>538334</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30749</t>
+          <t>29585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57089</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27896</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>51338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>98579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176735</t>
+          <t>179039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226425</t>
+          <t>224699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184837</t>
+          <t>185088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232925</t>
+          <t>230599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376317</t>
+          <t>375952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>441441</t>
+          <t>441947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65622</t>
+          <t>65373</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44319</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>71963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>125932</t>
+          <t>129585</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1723097</t>
+          <t>1732715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1845872</t>
+          <t>1847514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1785590</t>
+          <t>1788931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1906330</t>
+          <t>1907440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3542702</t>
+          <t>3554439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3717110</t>
+          <t>3715132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75541</t>
+          <t>76448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114887</t>
+          <t>114668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70247</t>
+          <t>71278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107926</t>
+          <t>109602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155648</t>
+          <t>155907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211342</t>
+          <t>209310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>909971</t>
+          <t>913816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1017363</t>
+          <t>1023601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1036809</t>
+          <t>1032092</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1151319</t>
+          <t>1147592</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1987661</t>
+          <t>1977026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2146987</t>
+          <t>2127141</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>487341</t>
+          <t>491340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>577691</t>
+          <t>575975</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>468625</t>
+          <t>471900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>557047</t>
+          <t>553808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>986121</t>
+          <t>988780</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1110421</t>
+          <t>1118834</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>341667</t>
+          <t>342398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>379545</t>
+          <t>380825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>548905</t>
+          <t>550182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>586267</t>
+          <t>587672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>906742</t>
+          <t>903758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>958219</t>
+          <t>958601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27318</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28303</t>
+          <t>28045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51070</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51422</t>
+          <t>52241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79077</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>61909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>86979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>120705</t>
+          <t>118787</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161555</t>
+          <t>157725</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53586</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85841</t>
+          <t>86095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78804</t>
+          <t>78619</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105317</t>
+          <t>105045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138435</t>
+          <t>137834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179563</t>
+          <t>180152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>925585</t>
+          <t>920143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1529108</t>
+          <t>1525930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1390340</t>
+          <t>1393306</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1697777</t>
+          <t>1708363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2875660</t>
+          <t>2875661</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2429843</t>
+          <t>2367200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3124718</t>
+          <t>3117734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72546</t>
+          <t>73610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>134986</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72773</t>
+          <t>75842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126804</t>
+          <t>124436</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>164291</t>
+          <t>163204</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>246047</t>
+          <t>241866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>378599</t>
+          <t>381405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1121251</t>
+          <t>1144894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231373</t>
+          <t>231738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>368036</t>
+          <t>369001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,17 +5589,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>918977</t>
+          <t>918978</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>689545</t>
+          <t>683512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1541014</t>
+          <t>1547823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5637,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167520</t>
+          <t>166338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280858</t>
+          <t>283270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200140</t>
+          <t>202820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501311</t>
+          <t>489713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>415698</t>
+          <t>411866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>743066</t>
+          <t>720097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>312395</t>
+          <t>319234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>368398</t>
+          <t>373034</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>299641</t>
+          <t>304505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347254</t>
+          <t>349242</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>634675</t>
+          <t>635128</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>703346</t>
+          <t>704250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64549</t>
+          <t>66272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97692</t>
+          <t>98456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75551</t>
+          <t>77148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106326</t>
+          <t>105897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151797</t>
+          <t>147937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195484</t>
+          <t>194838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143246</t>
+          <t>139831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190311</t>
+          <t>188214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153673</t>
+          <t>152776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193698</t>
+          <t>193114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305668</t>
+          <t>308665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366246</t>
+          <t>371133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -6093,12 +6093,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42905</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>75876</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56027</t>
+          <t>55878</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86144</t>
+          <t>85534</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>106061</t>
+          <t>105003</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152597</t>
+          <t>150021</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1509406</t>
+          <t>1603874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2231546</t>
+          <t>2233603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2301579</t>
+          <t>2292197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2635380</t>
+          <t>2641725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3907865</t>
+          <t>3965990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4714883</t>
+          <t>4732995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157134</t>
+          <t>154995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238284</t>
+          <t>236071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171224</t>
+          <t>175683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>244930</t>
+          <t>246621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>361683</t>
+          <t>364576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>468050</t>
+          <t>470304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>612407</t>
+          <t>617522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1512570</t>
+          <t>1457127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>458035</t>
+          <t>463647</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>623472</t>
+          <t>621863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1165073</t>
+          <t>1155482</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2190176</t>
+          <t>2032332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>280640</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>410386</t>
+          <t>414377</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>361612</t>
+          <t>361899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>688839</t>
+          <t>663606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>701246</t>
+          <t>687463</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1068259</t>
+          <t>1012501</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D$aparatos-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>687493</t>
+          <t>688244</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>743852</t>
+          <t>743903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>936918</t>
+          <t>933584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1000628</t>
+          <t>999241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1642012</t>
+          <t>1637760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1731713</t>
+          <t>1726840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35879</t>
+          <t>36493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23908</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49969</t>
+          <t>48474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171547</t>
+          <t>170094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224352</t>
+          <t>223229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>247026</t>
+          <t>247438</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305955</t>
+          <t>307389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>432370</t>
+          <t>435811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>512664</t>
+          <t>516876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36777</t>
+          <t>38732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66455</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59278</t>
+          <t>60223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94231</t>
+          <t>93693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105242</t>
+          <t>106690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147964</t>
+          <t>150382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1159409</t>
+          <t>1158298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1251990</t>
+          <t>1244517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1053440</t>
+          <t>1052475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1134474</t>
+          <t>1132851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2240524</t>
+          <t>2238963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2359704</t>
+          <t>2355361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52947</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>85619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34596</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62566</t>
+          <t>62308</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93732</t>
+          <t>95127</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136493</t>
+          <t>138705</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>569145</t>
+          <t>572518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>656831</t>
+          <t>656264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>507898</t>
+          <t>507977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>589311</t>
+          <t>583249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1099704</t>
+          <t>1104918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1216009</t>
+          <t>1218998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63163</t>
+          <t>64420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100173</t>
+          <t>99072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57759</t>
+          <t>58202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93195</t>
+          <t>93798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129786</t>
+          <t>130079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178446</t>
+          <t>178032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211979</t>
+          <t>211909</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>259054</t>
+          <t>256876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221471</t>
+          <t>221198</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>268407</t>
+          <t>266249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>446695</t>
+          <t>443933</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>510923</t>
+          <t>509056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43119</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>17251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41745</t>
+          <t>40434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71517</t>
+          <t>70485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183537</t>
+          <t>183231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229713</t>
+          <t>228974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160556</t>
+          <t>161552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208512</t>
+          <t>206692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>358819</t>
+          <t>362662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424221</t>
+          <t>425354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>19758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13934</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35192</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2101717</t>
+          <t>2096305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2215920</t>
+          <t>2217233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2249892</t>
+          <t>2248539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2369972</t>
+          <t>2366648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4383390</t>
+          <t>4383114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4550326</t>
+          <t>4548999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89084</t>
+          <t>90213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131649</t>
+          <t>130688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77250</t>
+          <t>79674</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117264</t>
+          <t>117639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176731</t>
+          <t>180205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233635</t>
+          <t>236211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>959363</t>
+          <t>956044</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1068243</t>
+          <t>1070480</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>949606</t>
+          <t>947091</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1058428</t>
+          <t>1058387</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1939503</t>
+          <t>1937323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2097597</t>
+          <t>2094777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117707</t>
+          <t>120021</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169531</t>
+          <t>171233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135971</t>
+          <t>137399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>187489</t>
+          <t>187394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,47 +2489,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>301691</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>266599</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>338334</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>301691</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>268874</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>341986</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>430610</t>
+          <t>432699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>484584</t>
+          <t>488083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>537821</t>
+          <t>533060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>602659</t>
+          <t>595673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>986725</t>
+          <t>983993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1068372</t>
+          <t>1069965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>21401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26736</t>
+          <t>27756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107717</t>
+          <t>107266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>145310</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>184771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>235142</t>
+          <t>238614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>303407</t>
+          <t>303727</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>371542</t>
+          <t>372536</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>142334</t>
+          <t>143771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189113</t>
+          <t>188121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180077</t>
+          <t>182056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233633</t>
+          <t>232295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>336252</t>
+          <t>335139</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404797</t>
+          <t>407277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1026113</t>
+          <t>1026507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1120548</t>
+          <t>1119016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>989696</t>
+          <t>988409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1077022</t>
+          <t>1078495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2048596</t>
+          <t>2044527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2174519</t>
+          <t>2171050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64865</t>
+          <t>63364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>52638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>67516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>104031</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>595116</t>
+          <t>597324</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>679906</t>
+          <t>682853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>634146</t>
+          <t>636410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>720271</t>
+          <t>724297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1253508</t>
+          <t>1255038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1374992</t>
+          <t>1373880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287533</t>
+          <t>287056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>354680</t>
+          <t>355565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217305</t>
+          <t>221840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278738</t>
+          <t>281012</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519531</t>
+          <t>522272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609436</t>
+          <t>611748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230561</t>
+          <t>231075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279126</t>
+          <t>281621</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224279</t>
+          <t>222633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>269498</t>
+          <t>270312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>468928</t>
+          <t>466411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>538334</t>
+          <t>535976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29585</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55830</t>
+          <t>56180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26467</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51338</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63649</t>
+          <t>64549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98579</t>
+          <t>98972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179039</t>
+          <t>176873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224699</t>
+          <t>226029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185088</t>
+          <t>184759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230599</t>
+          <t>231502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>375952</t>
+          <t>376961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>441947</t>
+          <t>444667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65373</t>
+          <t>66454</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>44243</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71963</t>
+          <t>73597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>88562</t>
+          <t>87514</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>129585</t>
+          <t>126872</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1732715</t>
+          <t>1728666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1847514</t>
+          <t>1848960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1788931</t>
+          <t>1789862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1907440</t>
+          <t>1904315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3554439</t>
+          <t>3545828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3715132</t>
+          <t>3723876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76448</t>
+          <t>77670</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114668</t>
+          <t>116521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71278</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109602</t>
+          <t>110313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155907</t>
+          <t>156691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209310</t>
+          <t>210080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>913816</t>
+          <t>913187</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1023601</t>
+          <t>1016860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1032092</t>
+          <t>1037862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1147592</t>
+          <t>1148511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1977026</t>
+          <t>1983790</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2127141</t>
+          <t>2143682</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>491340</t>
+          <t>491109</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>575975</t>
+          <t>578094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>471900</t>
+          <t>469694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>553808</t>
+          <t>553359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>988780</t>
+          <t>984658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1118834</t>
+          <t>1104253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -4837,32 +4837,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>362680</t>
+          <t>405702</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>342398</t>
+          <t>383893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380825</t>
+          <t>426853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4872,32 +4872,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>568757</t>
+          <t>615521</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>550182</t>
+          <t>596077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>587672</t>
+          <t>634248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4907,32 +4907,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>931437</t>
+          <t>1021224</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>903758</t>
+          <t>990076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>958601</t>
+          <t>1048134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>17886</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4985,32 +4985,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28045</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5020,22 +5020,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38974</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29364</t>
+          <t>32398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50056</t>
+          <t>53779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5063,32 +5063,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52241</t>
+          <t>54874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>87007</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5098,32 +5098,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73962</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61909</t>
+          <t>64392</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86979</t>
+          <t>90450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5133,32 +5133,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>138199</t>
+          <t>148209</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118787</t>
+          <t>127722</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>157725</t>
+          <t>170232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -5176,32 +5176,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68152</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>66926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86095</t>
+          <t>100853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5211,32 +5211,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91061</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78619</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105045</t>
+          <t>122942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5246,32 +5246,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>159213</t>
+          <t>187704</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137834</t>
+          <t>164624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180152</t>
+          <t>211926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -5293,32 +5293,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1348107</t>
+          <t>1464980</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920143</t>
+          <t>1410114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1525930</t>
+          <t>1518703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5328,32 +5328,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1527553</t>
+          <t>1444878</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1393306</t>
+          <t>1405211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1708363</t>
+          <t>1487048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,32 +5363,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2875661</t>
+          <t>2909859</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2367200</t>
+          <t>2843129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3117734</t>
+          <t>2975648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>104476</t>
+          <t>105889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73610</t>
+          <t>82829</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>127749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5441,32 +5441,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>103365</t>
+          <t>107424</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75842</t>
+          <t>90472</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124436</t>
+          <t>126082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5476,32 +5476,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>207841</t>
+          <t>213313</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>163204</t>
+          <t>187529</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>241866</t>
+          <t>245782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5519,32 +5519,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>600102</t>
+          <t>379258</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>381405</t>
+          <t>335678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1144894</t>
+          <t>424528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5554,32 +5554,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>318876</t>
+          <t>345336</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231738</t>
+          <t>315938</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>369001</t>
+          <t>379059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,32 +5589,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>918978</t>
+          <t>724594</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>683512</t>
+          <t>676536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1547823</t>
+          <t>777902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -5632,32 +5632,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>233623</t>
+          <t>272865</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166338</t>
+          <t>236681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283270</t>
+          <t>313187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5667,32 +5667,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>282914</t>
+          <t>268239</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202820</t>
+          <t>243517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>489713</t>
+          <t>299908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5702,32 +5702,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>516537</t>
+          <t>541103</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>411866</t>
+          <t>494998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>720097</t>
+          <t>593745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -5749,32 +5749,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>343848</t>
+          <t>376206</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>319234</t>
+          <t>348773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>373034</t>
+          <t>406619</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>325267</t>
+          <t>357101</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>304505</t>
+          <t>330320</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349242</t>
+          <t>378926</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5819,32 +5819,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>669115</t>
+          <t>733307</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>635128</t>
+          <t>695091</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>704250</t>
+          <t>770204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -5862,32 +5862,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80568</t>
+          <t>82637</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>67814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98456</t>
+          <t>100930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5897,32 +5897,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90485</t>
+          <t>98037</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77148</t>
+          <t>82592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105897</t>
+          <t>116855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5932,32 +5932,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>171053</t>
+          <t>180675</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147937</t>
+          <t>157087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194838</t>
+          <t>206637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5975,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>164628</t>
+          <t>176629</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139831</t>
+          <t>154660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188214</t>
+          <t>204281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6010,32 +6010,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>173286</t>
+          <t>194798</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152776</t>
+          <t>173958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193114</t>
+          <t>216911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6045,32 +6045,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>337915</t>
+          <t>371427</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308665</t>
+          <t>341584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371133</t>
+          <t>405966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -6088,32 +6088,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57579</t>
+          <t>76114</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75876</t>
+          <t>99032</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6123,32 +6123,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69265</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55878</t>
+          <t>67589</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>98383</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6158,32 +6158,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>126844</t>
+          <t>157948</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>105003</t>
+          <t>136255</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>150021</t>
+          <t>182087</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2054635</t>
+          <t>2246889</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1603874</t>
+          <t>2185001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2233603</t>
+          <t>2314271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6240,32 +6240,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2421577</t>
+          <t>2417501</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2292197</t>
+          <t>2362827</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2641725</t>
+          <t>2469674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6275,32 +6275,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4476212</t>
+          <t>4664390</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3965990</t>
+          <t>4577129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4732995</t>
+          <t>4745788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -6318,32 +6318,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202921</t>
+          <t>206412</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154995</t>
+          <t>178826</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>235916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6353,32 +6353,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175683</t>
+          <t>204327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246621</t>
+          <t>256819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6388,32 +6388,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>417867</t>
+          <t>434701</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364576</t>
+          <t>392575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>470304</t>
+          <t>470327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6431,32 +6431,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>828967</t>
+          <t>626486</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>617522</t>
+          <t>573629</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1457127</t>
+          <t>682473</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6466,32 +6466,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>566124</t>
+          <t>617744</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>463647</t>
+          <t>574952</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>621863</t>
+          <t>658238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6501,32 +6501,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1395091</t>
+          <t>1244230</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1155482</t>
+          <t>1185671</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2032332</t>
+          <t>1318201</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -6544,32 +6544,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>359354</t>
+          <t>431293</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>280640</t>
+          <t>392645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>414377</t>
+          <t>482274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6579,32 +6579,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>443240</t>
+          <t>455462</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>361899</t>
+          <t>418452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>663606</t>
+          <t>491589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6614,32 +6614,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>802593</t>
+          <t>886755</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>687463</t>
+          <t>833596</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1012501</t>
+          <t>945755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
